--- a/outputs/Block5_Election_Snapshot.xlsx
+++ b/outputs/Block5_Election_Snapshot.xlsx
@@ -58,28 +58,28 @@
     <t>Overall Diagnostic Stability</t>
   </si>
   <si>
-    <t>50.93%</t>
-  </si>
-  <si>
-    <t>46.15%</t>
+    <t>52.07%</t>
+  </si>
+  <si>
+    <t>45.01%</t>
   </si>
   <si>
     <t>2.92%</t>
   </si>
   <si>
-    <t>D 223 - R 212</t>
+    <t>D 219 - R 216</t>
   </si>
   <si>
     <t>Democratic</t>
   </si>
   <si>
-    <t>D 48 - R 52</t>
+    <t>D 50 - R 50</t>
   </si>
   <si>
     <t>Republican</t>
   </si>
   <si>
-    <t>64.0/100</t>
+    <t>70.0/100</t>
   </si>
 </sst>
 </file>
@@ -493,7 +493,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -501,7 +501,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -525,7 +525,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -533,7 +533,7 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:2">
